--- a/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="48">
   <si>
     <t>Mat</t>
   </si>
@@ -91,64 +91,76 @@
     <t>DIAZ</t>
   </si>
   <si>
+    <t>GARIBAY</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>JACINTO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>MONTERD</t>
   </si>
   <si>
-    <t>JACINTO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>AVALOS</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
+    <t>GARRIDO</t>
   </si>
   <si>
     <t>JUAN</t>
   </si>
   <si>
+    <t>LIZBETH MARIAM</t>
+  </si>
+  <si>
+    <t>SARA ALY</t>
+  </si>
+  <si>
+    <t>MATIAS</t>
+  </si>
+  <si>
+    <t>LUIS ALFREDO</t>
+  </si>
+  <si>
+    <t>ANGEL MOISES</t>
+  </si>
+  <si>
+    <t>IAN</t>
+  </si>
+  <si>
     <t>ISAI</t>
   </si>
   <si>
-    <t>MATIAS</t>
-  </si>
-  <si>
-    <t>MAXIMILIANO</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>SARA ALY</t>
-  </si>
-  <si>
-    <t>KRISTIAN YAEL</t>
+    <t>YOSELYN</t>
   </si>
 </sst>
 </file>
@@ -770,16 +782,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>82.5</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -793,16 +808,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>87.8</v>
+      </c>
+      <c r="H3">
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -816,16 +834,19 @@
         <v>48</v>
       </c>
       <c r="D4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.42</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -839,16 +860,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>86.48999999999999</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -885,16 +909,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>94.29000000000001</v>
+      </c>
+      <c r="H7">
+        <v>7.5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -982,7 +1009,7 @@
         <v>82.5</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -999,16 +1026,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>85.37</v>
+        <v>87.8</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1034,7 +1061,7 @@
         <v>85.42</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1051,16 +1078,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>78.38</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1103,16 +1130,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1148,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1186,10 +1213,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1203,16 +1230,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920281</v>
+        <v>24330051920345</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1226,16 +1253,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920049</v>
+        <v>24330051920040</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1249,7 +1276,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920057</v>
+        <v>24330051920049</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1258,7 +1285,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1272,7 +1299,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920083</v>
+        <v>24330051920312</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -1281,13 +1308,13 @@
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1295,7 +1322,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920040</v>
+        <v>24330051920324</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
@@ -1304,13 +1331,13 @@
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1318,7 +1345,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920054</v>
+        <v>24330051920325</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
@@ -1327,15 +1354,61 @@
         <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920281</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920120</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -88,40 +88,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>GARIBAY</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>JACINTO</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MONTERD</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
     <t>BALDERAS</t>
   </si>
   <si>
-    <t>AVALOS</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>TINOCO</t>
@@ -130,25 +124,16 @@
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>GARRIDO</t>
   </si>
   <si>
-    <t>JUAN</t>
-  </si>
-  <si>
     <t>LIZBETH MARIAM</t>
   </si>
   <si>
-    <t>SARA ALY</t>
-  </si>
-  <si>
     <t>MATIAS</t>
   </si>
   <si>
-    <t>LUIS ALFREDO</t>
+    <t>ANA KAREN</t>
   </si>
   <si>
     <t>ANGEL MOISES</t>
@@ -886,16 +871,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>93.94</v>
+      </c>
+      <c r="H6">
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -935,16 +923,19 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H8">
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1113,7 +1104,7 @@
         <v>93.94</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1156,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8">
-        <v>79.17</v>
+        <v>83.33</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1175,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1207,16 +1198,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920129</v>
+        <v>24330051920345</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1230,22 +1221,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920345</v>
+        <v>24330051920049</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1253,22 +1244,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920040</v>
+        <v>22330051920007</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1276,7 +1267,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920049</v>
+        <v>24330051920324</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1285,21 +1276,21 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920312</v>
+        <v>24330051920325</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -1308,36 +1299,36 @@
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920324</v>
+        <v>24330051920281</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1345,70 +1336,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920325</v>
+        <v>24330051920120</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920281</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920120</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="55">
   <si>
     <t>Mat</t>
   </si>
@@ -94,36 +94,60 @@
     <t>JACINTO</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MONTERD</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
     <t>BALDERAS</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>GARRIDO</t>
   </si>
   <si>
@@ -133,19 +157,31 @@
     <t>MATIAS</t>
   </si>
   <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>ANGEL MOISES</t>
+  </si>
+  <si>
+    <t>IAN</t>
+  </si>
+  <si>
+    <t>ISAI</t>
+  </si>
+  <si>
+    <t>YOSELYN</t>
+  </si>
+  <si>
     <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>ANGEL MOISES</t>
-  </si>
-  <si>
-    <t>IAN</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>YOSELYN</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1204,10 +1240,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1227,10 +1263,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1244,22 +1280,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920007</v>
+        <v>23330051920072</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1267,93 +1303,185 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920324</v>
+        <v>23330051920028</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920325</v>
+        <v>23330051920037</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920281</v>
+        <v>22330051920021</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920120</v>
+        <v>24330051920324</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920325</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920281</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>12</v>
       </c>
-      <c r="G8">
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920120</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920007</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="73">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,27 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
     <t>GARIBAY</t>
   </si>
   <si>
@@ -121,6 +142,21 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -133,9 +169,6 @@
     <t>RIVERA</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -149,6 +182,27 @@
   </si>
   <si>
     <t>GARRIDO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARA ALY</t>
+  </si>
+  <si>
+    <t>IVONNE ERIMAR</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>JUAN</t>
   </si>
   <si>
     <t>LIZBETH MARIAM</t>
@@ -1202,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1234,39 +1288,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920345</v>
+        <v>24330051920326</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920049</v>
+        <v>24330051920040</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1275,21 +1329,21 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920072</v>
+        <v>23330051920071</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1298,182 +1352,182 @@
         <v>15</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920028</v>
+        <v>24330051920233</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920037</v>
+        <v>24330051920338</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920021</v>
+        <v>24330051920335</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920324</v>
+        <v>24330051920129</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920325</v>
+        <v>24330051920345</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920281</v>
+        <v>24330051920049</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920120</v>
+        <v>23330051920072</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920007</v>
+        <v>23330051920028</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1482,6 +1536,167 @@
         <v>16</v>
       </c>
       <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920037</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920021</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920324</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920325</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920281</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920120</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920007</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="85">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,24 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>MACHORRO</t>
   </si>
   <si>
@@ -97,12 +115,6 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
@@ -142,12 +154,21 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -184,6 +205,24 @@
     <t>GARRIDO</t>
   </si>
   <si>
+    <t>AXEL BENITO</t>
+  </si>
+  <si>
+    <t>YERIEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ANGEL GAEL</t>
+  </si>
+  <si>
+    <t>YOSHUA RAFAEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
@@ -191,9 +230,6 @@
   </si>
   <si>
     <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
   </si>
   <si>
     <t>JONATHAN</t>
@@ -1256,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1288,16 +1324,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920326</v>
+        <v>24330051920329</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1311,22 +1347,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920040</v>
+        <v>24330051920145</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1334,22 +1370,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920071</v>
+        <v>24330051920348</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1357,68 +1393,68 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920233</v>
+        <v>24330051920375</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920338</v>
+        <v>24330051920259</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920335</v>
+        <v>24330051920233</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1426,22 +1462,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920129</v>
+        <v>24330051920326</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1449,68 +1485,68 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920345</v>
+        <v>24330051920040</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920049</v>
+        <v>23330051920071</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920072</v>
+        <v>24330051920338</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1518,22 +1554,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920028</v>
+        <v>24330051920335</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1541,22 +1577,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920037</v>
+        <v>24330051920129</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1564,22 +1600,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920021</v>
+        <v>24330051920345</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1587,108 +1623,108 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920324</v>
+        <v>24330051920049</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920325</v>
+        <v>23330051920072</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920281</v>
+        <v>23330051920028</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920120</v>
+        <v>23330051920037</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920007</v>
+        <v>22330051920021</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1697,6 +1733,121 @@
         <v>16</v>
       </c>
       <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920324</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920325</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920281</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920120</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920007</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="59">
   <si>
     <t>Mat</t>
   </si>
@@ -88,126 +88,75 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>DIAZ</t>
+    <t>JACINTO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>GARIBAY</t>
   </si>
   <si>
-    <t>JACINTO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MONTERD</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
     <t>MORA</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>MARCELINO</t>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GARRIDO</t>
-  </si>
-  <si>
-    <t>AXEL BENITO</t>
-  </si>
-  <si>
     <t>YERIEL</t>
   </si>
   <si>
@@ -217,61 +166,34 @@
     <t>ANGEL GAEL</t>
   </si>
   <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARA ALY</t>
+  </si>
+  <si>
     <t>YOSHUA RAFAEL</t>
   </si>
   <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARA ALY</t>
-  </si>
-  <si>
-    <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
     <t>JONATHAN</t>
   </si>
   <si>
     <t>JAVIER</t>
   </si>
   <si>
-    <t>JUAN</t>
+    <t>MATIAS</t>
+  </si>
+  <si>
+    <t>ANGEL MOISES</t>
+  </si>
+  <si>
+    <t>IAN</t>
   </si>
   <si>
     <t>LIZBETH MARIAM</t>
-  </si>
-  <si>
-    <t>MATIAS</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>IRVING</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>ANGEL MOISES</t>
-  </si>
-  <si>
-    <t>IAN</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>YOSELYN</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
   </si>
 </sst>
 </file>
@@ -1169,16 +1091,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G4">
-        <v>85.42</v>
+        <v>95.83</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1230,7 +1152,7 @@
         <v>93.94</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1247,16 +1169,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1273,16 +1195,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1292,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1324,16 +1246,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920329</v>
+        <v>24330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1347,22 +1269,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920145</v>
+        <v>24330051920348</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1370,22 +1292,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920348</v>
+        <v>24330051920375</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1393,68 +1315,68 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920375</v>
+        <v>24330051920233</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920259</v>
+        <v>24330051920326</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920233</v>
+        <v>24330051920040</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1462,22 +1384,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920326</v>
+        <v>24330051920259</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1485,7 +1407,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920040</v>
+        <v>24330051920338</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
@@ -1494,59 +1416,59 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920071</v>
+        <v>24330051920335</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920338</v>
+        <v>24330051920049</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1554,48 +1476,48 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920335</v>
+        <v>24330051920324</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920129</v>
+        <v>24330051920325</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1603,13 +1525,13 @@
         <v>24330051920345</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1618,236 +1540,6 @@
         <v>12</v>
       </c>
       <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920049</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920072</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920028</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920037</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920021</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920324</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920325</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920281</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>24330051920120</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920007</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -94,66 +94,21 @@
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
+    <t>GARIBAY</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>JACINTO</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GARIBAY</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -163,34 +118,7 @@
     <t>VALERIA</t>
   </si>
   <si>
-    <t>ANGEL GAEL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARA ALY</t>
-  </si>
-  <si>
     <t>YOSHUA RAFAEL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>MATIAS</t>
-  </si>
-  <si>
-    <t>ANGEL MOISES</t>
-  </si>
-  <si>
-    <t>IAN</t>
   </si>
   <si>
     <t>LIZBETH MARIAM</t>
@@ -1039,16 +967,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>82.5</v>
+        <v>95</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1065,16 +993,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>87.8</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1117,16 +1045,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>86.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1214,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1252,10 +1180,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1275,10 +1203,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1287,259 +1215,52 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920375</v>
+        <v>24330051920259</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920233</v>
+        <v>24330051920345</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920326</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920040</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920259</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920338</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920335</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920049</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920324</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920325</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920345</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>
